--- a/docs/forms/KKF_Fighter_Registration_Form.xlsx
+++ b/docs/forms/KKF_Fighter_Registration_Form.xlsx
@@ -1050,10 +1050,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$C$2:$C$26</formula1>
+    <dataValidation sqref="C7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
+      <formula1>Lists!$C$2:$C$26</formula1>
     </dataValidation>
-    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Date" error="Please enter a date, e.g. 14/05/2026." type="date" operator="between">
+    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date" error="Please enter a date, e.g. 14/05/2026." type="date" operator="between">
       <formula1>DATE(2020,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
@@ -3612,39 +3612,39 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
-      <formula1>=Lists!$A$2:$A$3</formula1>
+    <dataValidation sqref="E4 E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
+      <formula1>Lists!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 V4 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V35 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 V52 V53 AA4 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AA34 AA35 AA36 AA37 AA38 AA39 AA40 AA41 AA42 AA43 AA44 AA45 AA46 AA47 AA48 AA49 AA50 AA51 AA52 AA53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Date" error="Please enter a date as DD/MM/YYYY, e.g. 14/05/2003." type="date" operator="between">
+    <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 V4 V5 V6 V7 V8 V9 V10 V11 V12 V13 V14 V15 V16 V17 V18 V19 V20 V21 V22 V23 V24 V25 V26 V27 V28 V29 V30 V31 V32 V33 V34 V35 V36 V37 V38 V39 V40 V41 V42 V43 V44 V45 V46 V47 V48 V49 V50 V51 V52 V53 AA4 AA5 AA6 AA7 AA8 AA9 AA10 AA11 AA12 AA13 AA14 AA15 AA16 AA17 AA18 AA19 AA20 AA21 AA22 AA23 AA24 AA25 AA26 AA27 AA28 AA29 AA30 AA31 AA32 AA33 AA34 AA35 AA36 AA37 AA38 AA39 AA40 AA41 AA42 AA43 AA44 AA45 AA46 AA47 AA48 AA49 AA50 AA51 AA52 AA53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date" error="Please enter a date as DD/MM/YYYY, e.g. 14/05/2003." type="date" operator="between">
       <formula1>DATE(1950,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
     <dataValidation sqref="I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
-      <formula1>=Lists!$B$2:$B$7</formula1>
+      <formula1>Lists!$B$2:$B$7</formula1>
     </dataValidation>
-    <dataValidation sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
-      <formula1>=Lists!$C$2:$C$26</formula1>
+    <dataValidation sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
+      <formula1>Lists!$C$2:$C$26</formula1>
     </dataValidation>
-    <dataValidation sqref="K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 K52 K53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Number" error="Please enter a number from 40 to 150." type="decimal" operator="between">
+    <dataValidation sqref="K4 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 K23 K24 K25 K26 K27 K28 K29 K30 K31 K32 K33 K34 K35 K36 K37 K38 K39 K40 K41 K42 K43 K44 K45 K46 K47 K48 K49 K50 K51 K52 K53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Number" error="Please enter a number from 40 to 150." type="decimal" operator="between">
       <formula1>40</formula1>
       <formula2>150</formula2>
     </dataValidation>
-    <dataValidation sqref="M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Number" error="Please enter a number from 100 to 220." type="decimal" operator="between">
+    <dataValidation sqref="M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Number" error="Please enter a number from 100 to 220." type="decimal" operator="between">
       <formula1>100</formula1>
       <formula2>220</formula2>
     </dataValidation>
-    <dataValidation sqref="O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
-      <formula1>=Lists!$D$2:$D$3</formula1>
+    <dataValidation sqref="O4 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 O23 O24 O25 O26 O27 O28 O29 O30 O31 O32 O33 O34 O35 O36 O37 O38 O39 O40 O41 O42 O43 O44 O45 O46 O47 O48 O49 O50 O51 O52 O53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
+      <formula1>Lists!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 P52 P53 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 Q52 Q53 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Number" error="Please enter a number from 0 to 500." type="whole" operator="between">
+    <dataValidation sqref="P4 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 P23 P24 P25 P26 P27 P28 P29 P30 P31 P32 P33 P34 P35 P36 P37 P38 P39 P40 P41 P42 P43 P44 P45 P46 P47 P48 P49 P50 P51 P52 P53 Q4 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 Q23 Q24 Q25 Q26 Q27 Q28 Q29 Q30 Q31 Q32 Q33 Q34 Q35 Q36 Q37 Q38 Q39 Q40 Q41 Q42 Q43 Q44 Q45 Q46 Q47 Q48 Q49 Q50 Q51 Q52 Q53 R4 R5 R6 R7 R8 R9 R10 R11 R12 R13 R14 R15 R16 R17 R18 R19 R20 R21 R22 R23 R24 R25 R26 R27 R28 R29 R30 R31 R32 R33 R34 R35 R36 R37 R38 R39 R40 R41 R42 R43 R44 R45 R46 R47 R48 R49 R50 R51 R52 R53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Number" error="Please enter a number from 0 to 500." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>500</formula2>
     </dataValidation>
-    <dataValidation sqref="T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 T52 T53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
-      <formula1>=Lists!$E$2:$E$5</formula1>
+    <dataValidation sqref="T4 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22 T23 T24 T25 T26 T27 T28 T29 T30 T31 T32 T33 T34 T35 T36 T37 T38 T39 T40 T41 T42 T43 T44 T45 T46 T47 T48 T49 T50 T51 T52 T53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Please choose from the list." type="list">
+      <formula1>Lists!$E$2:$E$5</formula1>
     </dataValidation>
-    <dataValidation sqref="AD4 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33 AD34 AD35 AD36 AD37 AD38 AD39 AD40 AD41 AD42 AD43 AD44 AD45 AD46 AD47 AD48 AD49 AD50 AD51 AD52 AD53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$F$2:$F$3</formula1>
+    <dataValidation sqref="AD4 AD5 AD6 AD7 AD8 AD9 AD10 AD11 AD12 AD13 AD14 AD15 AD16 AD17 AD18 AD19 AD20 AD21 AD22 AD23 AD24 AD25 AD26 AD27 AD28 AD29 AD30 AD31 AD32 AD33 AD34 AD35 AD36 AD37 AD38 AD39 AD40 AD41 AD42 AD43 AD44 AD45 AD46 AD47 AD48 AD49 AD50 AD51 AD52 AD53" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>Lists!$F$2:$F$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
